--- a/PRD/QBot核心内测门禁Casebook_74条_2026-07-31.xlsx
+++ b/PRD/QBot核心内测门禁Casebook_74条_2026-07-31.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心内测Case" sheetId="1" r:id="R9976c185ac094a19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计总览" sheetId="2" r:id="R8b84f44a905945b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖矩阵" sheetId="3" r:id="Rb4400dd3f8204cab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="执行配置" sheetId="4" r:id="R3c0450e494f44069"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据与断言" sheetId="5" r:id="Rd6d95858234a43e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="旧Case审计" sheetId="6" r:id="R632315f857db40ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="旧Case收敛映射" sheetId="7" r:id="Rf681c6935dea4eb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MR与源码设计依据" sheetId="8" r:id="R36e0677c1df04125"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="生产灰度准入" sheetId="9" r:id="Re07f53cd70f8438e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心内测Case" sheetId="1" r:id="R6bd1759d3f9d4555"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计总览" sheetId="2" r:id="R72bd88b3fbab4635"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖矩阵" sheetId="3" r:id="R2ce8fa993d674e66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="执行配置" sheetId="4" r:id="R326edde214734117"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据与断言" sheetId="5" r:id="R1c8c748a484344bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="旧Case审计" sheetId="6" r:id="Rd933d470aa704295"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="旧Case收敛映射" sheetId="7" r:id="R1dc8b35d1bc84a82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MR与源码设计依据" sheetId="8" r:id="R8cb2c5e8f24744f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="生产灰度准入" sheetId="9" r:id="Rd0beeb57f22e40f8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6806,7 +6806,7 @@
         <x:v>BETA-EXPERT-002/007产出的研究专家已发布；依赖可用。</x:v>
       </x:c>
       <x:c r="J53" s="17" t="str">
-        <x:v>选择一个当天可验证的产品/行业问题；要求至少两个官方来源。</x:v>
+        <x:v>固定研究主题：截至2026-08-06，OpenAI Responses API 与 Chat Completions API 的官方定位、主要能力差异和迁移建议；要求至少两个可打开的 OpenAI 官方来源。</x:v>
       </x:c>
       <x:c r="K53" s="17" t="str">
         <x:v>1. 从专家详情召唤研究专家并核对exact release identity
@@ -6847,7 +6847,7 @@
         <x:v>[{"number":1,"action_id":"beta-expert-008-prepare","operation":"prepare","target":"BETA-EXPERT-008:prepare","declared_step":"按前置条件执行初始化、清理并校验fixture；原始步骤：从专家详情召唤研究专家并核对exact release identity","command":"prepare_expert_use","executor":"core-beta/scenario/beta-expert-008/v1","expected_state":"页面、发布身份、账号、fixture与执行策略全部ready","evidence_roles":["before_screenshot","action_receipt","after_screenshot"],"assertions":[{"id":"page-ready","path":"state.page.body_text_length","operator":"gte","expected":1}]},{"number":2,"action_id":"beta-expert-008-execute","operation":"execute","target":"BETA-EXPERT-008:execute","declared_step":"1. 从专家详情召唤研究专家并核对exact release identity；2. 完成检索和来源比较两轮，保存tools/call与来源；3. 第三轮形成带引用结论并核对最近召唤与task pin","command":"execute_expert_use","executor":"core-beta/scenario/beta-expert-008/v1","expected_state":"全部声明操作由对应真实UI/bridge/composer handler执行并生成动作回执","evidence_roles":["before_screenshot","action_receipt","after_screenshot"],"assertions":[{"id":"observable-assertion","path":"receipt.assertion_count","operator":"gte","expected":1}]},{"number":3,"action_id":"beta-expert-008-verify","operation":"verify","target":"BETA-EXPERT-008:verify","declared_step":"按taskId、能力identity、公开状态、完整回复、产物内容和负向边界执行精准断言与清理读回","command":"verify_expert_use","executor":"core-beta/scenario/beta-expert-008/v1","expected_state":"精准断言无失败且证据角色可生成不可变manifest","evidence_roles":["before_screenshot","action_receipt","after_screenshot"],"assertions":[{"id":"no-step-failure","path":"receipt.step_failures","operator":"equals","expected":0},{"id":"no-assertion-failure","path":"receipt.assertion_failures","operator":"equals","expected":0}]}]</x:v>
       </x:c>
       <x:c r="W53" s="17" t="str">
-        <x:v>[{"turn":1,"prompt":"检索两个官方来源说明目标问题现状。","oracle":"回复完整、与当前task及能力身份一致，并满足本Case精准断言","must_not_include":["traceback","DEEPBANK_","apiKey","Authorization: Bearer"]},{"turn":2,"prompt":"比较两份来源的共识、冲突和时效性。","oracle":"回复完整、与当前task及能力身份一致，并满足本Case精准断言","must_not_include":["traceback","DEEPBANK_","apiKey","Authorization: Bearer"]},{"turn":3,"prompt":"给出带引用的结论、风险和下一步。","oracle":"回复完整、与当前task及能力身份一致，并满足本Case精准断言","must_not_include":["traceback","DEEPBANK_","apiKey","Authorization: Bearer"]}]</x:v>
+        <x:v>[{"turn":1,"prompt":"检索至少两个 OpenAI 官方来源，说明截至2026-08-06 Responses API 与 Chat Completions API 的官方定位、主要能力差异和迁移建议；每个来源给出标题、日期或更新时间（如页面提供）及可打开 URL。","oracle":"回复完整、与当前task及能力身份一致，并满足本Case精准断言","must_not_include":["traceback","DEEPBANK_","apiKey","Authorization: Bearer"]},{"turn":2,"prompt":"仅基于上一轮的 OpenAI 官方来源，比较两者在工具能力、会话状态和迁移路径上的共识、差异与时效性，不得引入未引用来源。","oracle":"回复完整、与当前task及能力身份一致，并满足本Case精准断言","must_not_include":["traceback","DEEPBANK_","apiKey","Authorization: Bearer"]},{"turn":3,"prompt":"基于上述官方来源给出是否应优先迁移到 Responses API 的带引用结论、风险和下一步；逐条引用可打开 URL，并标明截至2026-08-06。","oracle":"回复完整、与当前task及能力身份一致，并满足本Case精准断言","must_not_include":["traceback","DEEPBANK_","apiKey","Authorization: Bearer"]}]</x:v>
       </x:c>
       <x:c r="X53" s="17"/>
       <x:c r="Y53" s="17" t="str">
